--- a/batcaverna/planilhas/kanban.xlsx
+++ b/batcaverna/planilhas/kanban.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,7 +427,7 @@
         <v>UFF - Minicurso Circuitos Eletricos CC</v>
       </c>
       <c r="B2" t="str">
-        <v>to do</v>
+        <v>in progress</v>
       </c>
       <c r="C2" t="str">
         <v>868d3j5vf</v>
@@ -439,7 +439,7 @@
         <v>09/01/2024</v>
       </c>
       <c r="F2" t="str">
-        <v>17/07/2026</v>
+        <v>16/09/2026</v>
       </c>
       <c r="G2" t="str" xml:space="preserve">
         <v xml:space="preserve"># TCC Pedro Victor
@@ -1651,7 +1651,7 @@
         <v>UFF 2026.1</v>
       </c>
       <c r="B10" t="str">
-        <v>in progress</v>
+        <v>to do</v>
       </c>
       <c r="C10" t="str">
         <v>1768855939861</v>
@@ -1663,7 +1663,7 @@
         <v>19/01/2026</v>
       </c>
       <c r="F10" t="str">
-        <v>20/07/2026</v>
+        <v>16/10/2026</v>
       </c>
       <c r="G10" t="str" xml:space="preserve">
         <v xml:space="preserve">---
@@ -1767,117 +1767,97 @@
         <v>19/01/2026</v>
       </c>
       <c r="F11" t="str">
-        <v>18/07/2026</v>
+        <v>16/10/2026</v>
       </c>
       <c r="G11" t="str" xml:space="preserve">
-        <v xml:space="preserve"># Cienstista de Dados_x000d__x000d_
----_x000d__x000d_
-_x000d__x000d_
-  __Atividades Práticas: ETL com Python, PySpark + SQL + Pandas para machine learning e relatórios automatizados___x000d__x000d_
-_x000d__x000d_
-- Projeto 1 - Pipeline de Exploração de Dados e Operações SQL com Spark SQL_x000d__x000d_
-- Projeto 2 - Banco de Dados, Machine Learning e Pipeline ETL em Cluster Spark Para Detectar Anomalias em Transações Financeiras_x000d__x000d_
-- Projeto 3 - Pipeline de Machine Learning em Cluster Spark Para Previsão de Churn - Treinamento e Deploy_x000d__x000d_
-- Projeto 4 - Pipeline de Pré-Processamento, Validação Cruzada e Otimização em Machine Learning_x000d__x000d_
-- Projeto 5 - Otimização de Pipeline ETL e Machine Learning com PySpark_x000d__x000d_
-- Projeto 6 - Pipeline de Coleta, Transformação e Modelagem Preditiva em Tempo Real com Spark Streaming e TensorFlow_x000d__x000d_
-- Projeto 7 - Data Lakehouse Time Travel com Apache Spark e Delta Lake_x000d__x000d_
-- Projeto 8 - Deploy e Inferência de Modelos de Machine Learning com MLflow e Databricks_x000d__x000d_
-_x000d__x000d_
-- [ ] Planejamento de horários de aulas_x000d__x000d_
-- [ ] Livros:_x000d__x000d_
-_x000d__x000d_
-_x000d__x000d_
-## Roadmap Cientista de Dados_x000d__x000d_
-_x000d__x000d_
-![alt text - ciencia de dados ONS](image-1.png)_x000d__x000d_
-_x000d__x000d_
-## Checklist de conhecimentos_x000d__x000d_
-_x000d__x000d_
-- [x] Pandas_x000d__x000d_
-- [ ] SQL_x000d__x000d_
-- [x] Streamlit_x000d__x000d_
-- [ ] Quarto Relatorios automatizados_x000d__x000d_
-- [ ] pyspark_x000d__x000d_
-- [ ] Algoritimos de ML e DL_x000d__x000d_
-- [ ] Projetos com base de dados publicas_x000d__x000d_
-- [ ] Modelagem de DB_x000d__x000d_
-- [ ] ETL - Python com PDF, Word e Excel_x000d__x000d_
-- [ ] Scripts e rotinas que substituem formulas do excel _x000d__x000d_
-_x000d__x000d_
-##  ONS, Pesquisa Científica e Cientista de dados_x000d__x000d_
-_x000d__x000d_
-- [ ] CIENTISTA DE DADOS - ML E DATASET ENERGY + CLASSIFICATION + REGRESSION + KMEANS_x000d__x000d_
-_x000d__x000d_
-## Projetos com Datasets de orgãos publicos_x000d__x000d_
-_x000d__x000d_
-- [x] Dashboard analise distribuição energético ONS + SIN - Website para leigos_x000d__x000d_
-- [ ] dados publicos gov br_x000d__x000d_
-- [ ] Dados ONS_x000d__x000d_
-- [ ] Dados Kaggle_x000d__x000d_
-- [ ] Dados imagens de Satélites_x000d__x000d_
-_x000d__x000d_
-_x000d__x000d_
----_x000d__x000d_
-# Checklist de Metas: Trilha Fullstack &amp; Desktop (Python, JS, Rust)_x000d__x000d_
----_x000d__x000d_
-_x000d__x000d_
-Este checklist visa integrar as tecnologias mencionadas (Flask, Pandas, PySide6, NextJS, Tauri, Rust) em projetos práticos de complexidade crescente._x000d__x000d_
-_x000d__x000d_
-## Fase 1: Backend &amp; Processamento de Dados (Python)_x000d__x000d_
-_x000d__x000d_
-Foco: Flask, Pandas, Modelagem de Dados, API REST._x000d__x000d_
-_x000d__x000d_
-- [ ] **Projeto 1: API de Análise de Dados (Simples)**_x000d__x000d_
-  - *Stack:* Flask, Pandas._x000d__x000d_
-  - *Objetivo:* Criar uma rota POST que recebe um arquivo CSV/JSON, processa estatísticas básicas (média, mediana, desvio padrão) com Pandas e retorna um JSON com os resultados._x000d__x000d_
-- [ ] **Projeto 2: Sistema de Gestão de Inventário (CRUD REST)**_x000d__x000d_
-  - *Stack:* Flask, SQLAlchemy (ou outro ORM), SQLite/Postgres._x000d__x000d_
-  - *Objetivo:* Criar uma API REST completa com autenticação básica. Rotas para criar, ler, atualizar e deletar produtos._x000d__x000d_
-  - *Meta:* Implementar validação de dados (Pydantic ou Marshmallow)._x000d__x000d_
-_x000d__x000d_
-## Fase 2: Desktop Nativo &amp; GUI (Python)_x000d__x000d_
-_x000d__x000d_
-Foco: PySide6 (Qt for Python)._x000d__x000d_
-_x000d__x000d_
-- [ ] **Projeto 3: Dashboard de Monitoramento de Sistema**_x000d__x000d_
-  - *Stack:* PySide6, psutil._x000d__x000d_
-  - *Objetivo:* Criar uma janela desktop que mostra uso de CPU, RAM e Disco em tempo real usando gráficos (PyQtGraph ou Matplotlib integrado)._x000d__x000d_
-- [ ] **Projeto 4: Cliente Desktop para Inventário**_x000d__x000d_
-  - *Stack:* PySide6, requests._x000d__x000d_
-  - *Objetivo:* Criar uma interface gráfica que consome a API do *Projeto 2*. O usuário deve poder adicionar e ver produtos através do app desktop._x000d__x000d_
-_x000d__x000d_
-## Fase 3: Frontend Web Moderno (JavaScript/TypeScript)_x000d__x000d_
-_x000d__x000d_
-Foco: NextJS, React, TailwindCSS._x000d__x000d_
-_x000d__x000d_
-- [ ] **Projeto 5: Landing Page de Portfólio**_x000d__x000d_
-  - *Stack:* NextJS, TailwindCSS._x000d__x000d_
-  - *Objetivo:* Site estático simples para listar seus projetos do GitHub (pode consumir a API do GitHub)._x000d__x000d_
-- [ ] **Projeto 6: Dashboard Web Analytics**_x000d__x000d_
-  - *Stack:* NextJS, Chart.js (ou Recharts)._x000d__x000d_
-  - *Objetivo:* Consumir a API do *Projeto 1* ou *Projeto 2* e exibir os dados em gráficos interativos no navegador._x000d__x000d_
-_x000d__x000d_
-## Fase 4: O Próximo Nível - Performance &amp; Apps Híbridos (Rust &amp; Tauri)_x000d__x000d_
-_x000d__x000d_
-Foco: Rust básico, Tauri (Unindo o Frontend Web com Backend Nativo)._x000d__x000d_
-_x000d__x000d_
-- [ ] **Projeto 7: "Hello World" em Rust CLI**_x000d__x000d_
-  - *Stack:* Rust (Cargo)._x000d__x000d_
-  - *Objetivo:* Criar uma ferramenta CLI simples em Rust que lê um arquivo de texto e conta as palavras (reimplementação simples do `wc`)._x000d__x000d_
-- [ ] **Projeto 8: App de Notas Seguro (Tauri)**_x000d__x000d_
-  - *Stack:* Tauri, Rust (Backend), React/NextJS (Frontend)._x000d__x000d_
-  - *Objetivo:* Um aplicativo desktop onde o frontend (JS) envia notas para o backend (Rust) salvar arquivos criptografados no disco._x000d__x000d_
-  - *Meta:* Aprender a comunicação IPC (Frontend &lt;-&gt; Backend) no Tauri._x000d__x000d_
-_x000d__x000d_
-## Fase 5: O Projeto Integrador (Master)_x000d__x000d_
-_x000d__x000d_
-- [ ] **Projeto Final: A Suíte de Produtividade**_x000d__x000d_
-  - *Backend Central:* API Flask com Pandas para relatórios pesados._x000d__x000d_
-  - *App Desktop Leve:* Tauri App (Rust+React) para uso diário e widgets._x000d__x000d_
-  - *App Admin:* PySide6 para configurações avançadas do sistema local._x000d__x000d_
-_x000d__x000d_
----_x000d__x000d_
+        <v xml:space="preserve"># Cienstista de Dados
+- datascienceacademy.com.br
+## Dicas para acelerar o aprendizado
+- O cerebro humano deve estar exposto a um conceito várias e várias vezes, de formas diferentes, para que realmente possa compreende-lo
+- Se um conceito não ficar claro em um primeiro momento, anote sua dúvida para visitá-la depois
+- A medida que voce avança no curso, é importante manter um registro do seu progresso e das áreas que exigem mais atenção
+- Mantenha seu diário de bordo e caderno de equações para anotas ideias, conceitos e resumos de cada capítulo e questões para exercitar 
+- Errar faz parte do processo, cada erro é uma oportunidade para aprimorar sua compreensão e aprimorar as habilidades
+- A prática ativa não só reforça o aprendizado, mas também ajuda a identificar áreas que voce pode não ter compreendido completamente.  Aplique os conceitos aprendidos em pequenos projetos, modificar os projetos e pesquisa em sites de empresa para identificar quais projetos poderiam ajudar, gerar dados de exemplos e então resolver o problema usando o conhecimento de cientista de dados
+- É fundamental ter uma rotina de autoavaliação continuada por meio de testes, simulados e projetos. Reflita sempre sobre o que está aprendendo, como aquilo pode ser aplicado no dia a dia, conecte o que aprendeu com a experiencia que voce possui em outras áreas e faça a sua pesquisa complementar, crie jupyter notebooks, relatórios em Quarto e pubique todos no seu blog, linkedin e Lattes.
+---
+# Projetos DSA
+- [ ] Atividades PLC ONS: ETL com Python, PySpark + SQL + Pandas para machine learning e relatórios automatizados
+- Projeto 1 - Pipeline de Exploração de Dados e Operações SQL com Spark SQL
+- Projeto 2 - Banco de Dados, Machine Learning e Pipeline ETL em Cluster Spark Para Detectar Anomalias em Transações Financeiras
+- Projeto 3 - Pipeline de Machine Learning em Cluster Spark Para Previsão de Churn - Treinamento e Deploy
+- Projeto 4 - Pipeline de Pré-Processamento, Validação Cruzada e Otimização em Machine Learning
+- Projeto 5 - Otimização de Pipeline ETL e Machine Learning com PySpark
+- Projeto 6 - Pipeline de Coleta, Transformação e Modelagem Preditiva em Tempo Real com Spark Streaming e TensorFlow
+- Projeto 7 - Data Lakehouse Time Travel com Apache Spark e Delta Lake
+- Projeto 8 - Deploy e Inferência de Modelos de Machine Learning com MLflow e Databricks
+- [ ] Planejamento de horários de aulas
+- [ ] Livros:
+## Roadmap Cientista de Dados
+![alt text - ciencia de dados ONS](image-1.png)
+## Checklist de conhecimentos
+- [x] Pandas
+- [ ] SQL
+- [x] Streamlit
+- [ ] Quarto Relatorios automatizados
+- [ ] pyspark
+- [ ] Algoritimos de ML e DL
+- [ ] Projetos com base de dados publicas
+- [ ] Modelagem de DB
+- [ ] ETL - Python com PDF, Word e Excel
+- [ ] Scripts e rotinas que substituem formulas do excel 
+##  ONS, Pesquisa Científica e Cientista de dados
+- [ ] CIENTISTA DE DADOS - ML E DATASET ENERGY + CLASSIFICATION + REGRESSION + KMEANS
+## Projetos com Datasets de orgãos publicos
+- [x] Dashboard analise distribuição energético ONS + SIN - Website para leigos
+- [ ] dados publicos gov br
+- [ ] Dados ONS
+- [ ] Dados Kaggle
+- [ ] Dados imagens de Satélites
+---
+# Checklist de Metas: Trilha Fullstack &amp; Desktop (Python, JS, Rust)
+---
+Este checklist visa integrar as tecnologias mencionadas (Flask, Pandas, PySide6, NextJS, Tauri, Rust) em projetos práticos de complexidade crescente.
+## Fase 1: Backend &amp; Processamento de Dados (Python)
+Foco: Flask, Pandas, Modelagem de Dados, API REST.
+- [ ] **Projeto 1: API de Análise de Dados (Simples)**
+  - *Stack:* Flask, Pandas.
+  - *Objetivo:* Criar uma rota POST que recebe um arquivo CSV/JSON, processa estatísticas básicas (média, mediana, desvio padrão) com Pandas e retorna um JSON com os resultados.
+- [ ] **Projeto 2: Sistema de Gestão de Inventário (CRUD REST)**
+  - *Stack:* Flask, SQLAlchemy (ou outro ORM), SQLite/Postgres.
+  - *Objetivo:* Criar uma API REST completa com autenticação básica. Rotas para criar, ler, atualizar e deletar produtos.
+  - *Meta:* Implementar validação de dados (Pydantic ou Marshmallow).
+## Fase 2: Desktop Nativo &amp; GUI (Python)
+Foco: PySide6 (Qt for Python).
+- [ ] **Projeto 3: Dashboard de Monitoramento de Sistema**
+  - *Stack:* PySide6, psutil.
+  - *Objetivo:* Criar uma janela desktop que mostra uso de CPU, RAM e Disco em tempo real usando gráficos (PyQtGraph ou Matplotlib integrado).
+- [ ] **Projeto 4: Cliente Desktop para Inventário**
+  - *Stack:* PySide6, requests.
+  - *Objetivo:* Criar uma interface gráfica que consome a API do *Projeto 2*. O usuário deve poder adicionar e ver produtos através do app desktop.
+## Fase 3: Frontend Web Moderno (JavaScript/TypeScript)
+Foco: NextJS, React, TailwindCSS.
+- [ ] **Projeto 5: Landing Page de Portfólio**
+  - *Stack:* NextJS, TailwindCSS.
+  - *Objetivo:* Site estático simples para listar seus projetos do GitHub (pode consumir a API do GitHub).
+- [ ] **Projeto 6: Dashboard Web Analytics**
+  - *Stack:* NextJS, Chart.js (ou Recharts).
+  - *Objetivo:* Consumir a API do *Projeto 1* ou *Projeto 2* e exibir os dados em gráficos interativos no navegador.
+## Fase 4: O Próximo Nível - Performance &amp; Apps Híbridos (Rust &amp; Tauri)
+Foco: Rust básico, Tauri (Unindo o Frontend Web com Backend Nativo).
+- [ ] **Projeto 7: "Hello World" em Rust CLI**
+  - *Stack:* Rust (Cargo).
+  - *Objetivo:* Criar uma ferramenta CLI simples em Rust que lê um arquivo de texto e conta as palavras (reimplementação simples do `wc`).
+- [ ] **Projeto 8: App de Notas Seguro (Tauri)**
+  - *Stack:* Tauri, Rust (Backend), React/NextJS (Frontend).
+  - *Objetivo:* Um aplicativo desktop onde o frontend (JS) envia notas para o backend (Rust) salvar arquivos criptografados no disco.
+  - *Meta:* Aprender a comunicação IPC (Frontend &lt;-&gt; Backend) no Tauri.
+## Fase 5: O Projeto Integrador (Master)
+- [ ] **Projeto Final: A Suíte de Produtividade**
+  - *Backend Central:* API Flask com Pandas para relatórios pesados.
+  - *App Desktop Leve:* Tauri App (Rust+React) para uso diário e widgets.
+  - *App Admin:* PySide6 para configurações avançadas do sistema local.
+---
 </v>
       </c>
     </row>
@@ -1886,7 +1866,7 @@
         <v xml:space="preserve">ESTUDOS - Quizz App with AI </v>
       </c>
       <c r="B12" t="str">
-        <v>projetos parados</v>
+        <v>to do</v>
       </c>
       <c r="C12" t="str">
         <v>1770229463843</v>
@@ -1898,7 +1878,7 @@
         <v>04/02/2026</v>
       </c>
       <c r="F12" t="str">
-        <v>25/07/2026</v>
+        <v>16/10/2026</v>
       </c>
       <c r="G12" t="str" xml:space="preserve">
         <v xml:space="preserve">_x000d__x000d_
@@ -1973,7 +1953,7 @@
         <v>UFF - Estudos Circuitos CA e Eletromagnetismo (Física 2)</v>
       </c>
       <c r="B14" t="str">
-        <v>ONS - PLC - 2026</v>
+        <v>to do</v>
       </c>
       <c r="C14" t="str">
         <v>1770831390907</v>
@@ -1985,7 +1965,7 @@
         <v>11/02/2026</v>
       </c>
       <c r="F14" t="str">
-        <v>10/06/2026</v>
+        <v>05/08/2026</v>
       </c>
       <c r="G14" t="str" xml:space="preserve">
         <v xml:space="preserve">Curso completo de Eletrônica Analógica Básica
@@ -2328,7 +2308,7 @@
         <v>11/03/2026</v>
       </c>
       <c r="F15" t="str">
-        <v>03/06/2026</v>
+        <v>16/10/2026</v>
       </c>
       <c r="G15" t="str" xml:space="preserve">
         <v xml:space="preserve">---
@@ -2521,15 +2501,40 @@
 - [x] Engenheiro de Software Pleno - Legado PVRV: Py, JS, C++, Dart e Rust. Anotações para perspectiva de carreira com 28 anos em site que ajuda a priorizar os projetos.
 - [x] Backup Kanban, Batcaverna, Linux e Win11
 - [x] Listagem de projetos atuais por tecnologias do github
-- [x] Juntar todos sites estaticos em HTML que tenho num unico projeto NextJS com rotas e MVC (Gohan Treinamentos, Legado PVRV, Pomodoro)</v>
+- [x] Juntar todos sites estaticos em HTML que tenho num unico projeto NextJS com rotas e MVC (Gohan Treinamentos, Legado PVRV, Pomodoro)
+---
+# Concluidos 2026 - Outubro (16-10-2026)
+- [x] HTML templates para Gohan Treinamentos Refatorado com SOLID, MVC e framework CSS components
+- [x] Juntar todos sites estaticos em HTML que tenho num unico projeto NextJS com rotas e MVC (Gohan Treinamentos, Legado PVRV, Pomodoro)
+- [x] Kanban, Scrum, Planejamento e metas (Segunda e sexta)
+- [x] Organização de arquivos .MD
+- [x] Organização projetos Github
+- [x] Update Diagrama Organon 440KV - Completo
+- [x] Organização de Word e Excel usados para a semana no ONS
+- [x] Pyside6 x Tauri x Flutter - projetos desktop
+- [x] NextJS x Astro - projetos web
+- [x] Organização e planejamento de Automaçôes ONS PLC 2026
+- [x] Resolver sistema de solver de calculadora de EDO e Matrizes com plots em Qt6(sympy)
+- [x] Plot função (matplotlib)
+- [x] Integrar no PySide6
+- [x] Circuitos Digitais P1 (Karnaugh, SOP, teoremas booleanos)
+- [x] ONS (Python + relatórios + checklist)
+- [x] Projetos (calculadora + Organon + Pyside6)
+- [x] P1 circuitos digitais
+- [x] P1 Circuitos Eletricos CC
+- [x] P2 Circuitos Eletricos CC
+- [x] Plotagem dos valores de geração em KWH de 2023 até 2026
+- [x] Projeção do grafico com derivdas
+- [x] taxa de rendimento do salario ONS com 5% e 10% ao mes
+- [x] Conta de luz com plots em Julia e Python e otimização com derivada de conta de luz</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
       <c r="A16" t="str">
-        <v>Estudos Circuitos Digitais - UFF</v>
+        <v>Estudos  - UFF 2026.2</v>
       </c>
       <c r="B16" t="str">
-        <v>projetos parados</v>
+        <v>in progress</v>
       </c>
       <c r="C16" t="str">
         <v>1773749887529</v>
@@ -2541,7 +2546,7 @@
         <v>17/03/2026</v>
       </c>
       <c r="F16" t="str">
-        <v>30/07/2026</v>
+        <v>16/10/2026</v>
       </c>
       <c r="G16" t="str" xml:space="preserve">
         <v xml:space="preserve">## Circuitos Digitais P1
@@ -2573,18 +2578,7 @@
   - SR
   - D
   - T
-- [ ] Diagrama Borda de Subida x Descida (Tipo de clock)
-- [ ] Contador decimal - binario com 4 FF JK
-- [ ] Contador decimal - binario com 4 FF JK
-- [ ] Contador decimal - binario com 4 FF JK
 - [ ] Contadores e Registradores
----
-## Estudos UFF 2026.1
-- [ ] Impedancia complexa
-- [ ] Reatancia capactitiva
-- [ ] Reatnacia indutiva
-- [ ] Teorema de Thevenin e Norton
-- [ ] Max. Transferência de Potência 
 ---
 # EMENTA
 ---
@@ -2672,7 +2666,7 @@
         <v>Projetos Desktop PLC ONS 2026</v>
       </c>
       <c r="B17" t="str">
-        <v>projetos parados</v>
+        <v>to do</v>
       </c>
       <c r="C17" t="str">
         <v>1773751533960</v>
@@ -2684,7 +2678,7 @@
         <v>17/03/2026</v>
       </c>
       <c r="F17" t="str">
-        <v>25/07/2026</v>
+        <v>20/08/2026</v>
       </c>
       <c r="G17" t="str" xml:space="preserve">
         <v xml:space="preserve">
@@ -2855,7 +2849,7 @@
         <v>Ementas - UFF</v>
       </c>
       <c r="B19" t="str">
-        <v>testing</v>
+        <v>to do</v>
       </c>
       <c r="C19" t="str">
         <v>1777067813617</v>
@@ -2867,7 +2861,7 @@
         <v>24/04/2026</v>
       </c>
       <c r="F19" t="str">
-        <v>17/07/2026</v>
+        <v>16/10/2026</v>
       </c>
       <c r="G19" t="str" xml:space="preserve">
         <v xml:space="preserve">
@@ -3292,7 +3286,7 @@
         <v xml:space="preserve">Relatórios PDF, OverLeaf, Quarto e Artigos Científicos </v>
       </c>
       <c r="B21" t="str">
-        <v>ONS - PLC - 2026</v>
+        <v>to do</v>
       </c>
       <c r="C21" t="str">
         <v>1778242830252</v>
@@ -3304,7 +3298,7 @@
         <v>08/05/2026</v>
       </c>
       <c r="F21" t="str">
-        <v>10/06/2026</v>
+        <v>05/08/2026</v>
       </c>
       <c r="G21" t="str" xml:space="preserve">
         <v xml:space="preserve"># Novo Item
@@ -3316,7 +3310,7 @@
         <v>Programação Backend Python e C++</v>
       </c>
       <c r="B22" t="str">
-        <v>in progress</v>
+        <v>to do</v>
       </c>
       <c r="C22" t="str">
         <v>1780105879769</v>
@@ -3328,7 +3322,7 @@
         <v>29/05/2026</v>
       </c>
       <c r="F22" t="str">
-        <v>30/07/2026</v>
+        <v>16/09/2026</v>
       </c>
       <c r="G22" t="str" xml:space="preserve">
         <v xml:space="preserve"># Python (Flask, FastAPI, Tornado) e C++ com Drogon  
@@ -3644,7 +3638,7 @@
         <v>30/07/2026</v>
       </c>
       <c r="F27" t="str">
-        <v>30/07/2026</v>
+        <v>16/09/2026</v>
       </c>
       <c r="G27" t="str" xml:space="preserve">
         <v xml:space="preserve"># Curso: INTELIGÊNCIA ARTIFICIAL E CIÊNCIA DE DADOS
@@ -3699,9 +3693,284 @@
 </v>
       </c>
     </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>Estatistica para Ciencia de Dados</v>
+      </c>
+      <c r="B28" t="str">
+        <v>to do</v>
+      </c>
+      <c r="C28" t="str">
+        <v>1785951514953</v>
+      </c>
+      <c r="D28" t="str">
+        <v>uff</v>
+      </c>
+      <c r="E28" t="str">
+        <v>05/08/2026</v>
+      </c>
+      <c r="F28" t="str">
+        <v>05/08/2026</v>
+      </c>
+      <c r="G28" t="str" xml:space="preserve">
+        <v xml:space="preserve">## Base de dados publicas
+- NASA
+- Pokemon
+- Fifa 19 players dataset
+- Campeonato brasileiro e libertadores
+- Copa do Mundo 2026
+- ONS: Carga e Geração em tempo real
+- ONS: planejamento energetico PLC
+- ONS: Linhas de transmissão e Usinas Geradoras com redespacho de UEO e UFV
+- AstroPY
+- Sensoriamento Remoto - Localizacao de incendios, acidentes e enchente de agua da chuva em tempo real
+## Datasets
+## backend developer MVC
+## Dashboard Frontned com Plotly em Python e Simulações matemáticas em Julia
+## Estatistica I e II
+## Metodos de fisica experimental (livro)
+## Estatiística Descritiva (CONCEITOS BÁSICOS E FUNDAMENTOS)
+### Dados Tabulares
+- Média
+- Moda
+- min e max (otimização)
+- Derivdas Parciais e Integral 
+- Variancia e Desvio Padrao
+- Quaril / percentil
+- Correlação X Causalidade
+### Plotagem de Gráficos
+- Barras (colunas ou empilhadas)
+- Linhas
+- Pizza
+- Pontos
+- Cascata
+- Google Maps
+- Mapa de Calor
+- Graficod de Bode
+- Plotagem em 3D de forças vetoriais
+- Plotagem de simulações do plano Real e Imaginario e Sistemas Dinamicos ou usando variaveis discretas 
+### Estatística Ingerencial
+- Teste A/B
+- Probabilidade
+- Intervalos de Confiança
+- Teorema da amostragem
+- Design de experimentos e testes de hipoteses como cientista Galileu e Newton
+### Estatística Bayesiana
+- Regra de Bayes
+- 
+</v>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>Agente de IA - Sergio Sacani</v>
+      </c>
+      <c r="B29" t="str">
+        <v>projetos parados</v>
+      </c>
+      <c r="C29" t="str">
+        <v>1787112771173</v>
+      </c>
+      <c r="D29" t="str">
+        <v>ons</v>
+      </c>
+      <c r="E29" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="F29" t="str">
+        <v>20/08/2026</v>
+      </c>
+      <c r="G29" t="str" xml:space="preserve">
+        <v xml:space="preserve">## Ferramentas
+- n8n
+- chatgpt x gemini x chatmaritaca
+- google sheets, word, PDF e Gmail
+Módulo 01
+As Grandes Ondas da Inteligência Artificial 
+Entenda a evolução da IA ao longo do tempo, de Turing até os dias de hoje. Você vai entender por que usar IA é mais importante do que nunca.
+Módulo 02
+Primeiros Passos na IA Generativa
+Esse módulo dará a você toda a clareza necessária para tirar o melhor proveito das IAs. Tudo com linguagem acessível e exemplos práticos.
+Módulo 03
+Produtividade Pessoal com Claude
+Como usar o Claude para criar projetos, integrar com ferramentas do Google, gerar relatório, criar dashboards interativos e fazer pesquisas profundas.
+Módulo 04
+Introdução às automações no N8N
+Como montar gatilhos, ações e condições no n8n, sem escrever nenhuma linha de código.  Mais a base de dados que conecta tudo: Postgres, Supabase, Redis e OpenAI.
+Módulo 05
+Seu primeiro agente funcionando em 1 hora 
+Construa um assistente pessoal que registra seus gastos e receitas via mensagem no WhatsApp - e prove para si mesmo que pode você criar agentes 
+Módulo 06
+Fundamentos de marketing e vendas 
+Esqueça a automatização de projetos que não dão ROI imediato e foque no que mais gera dinheiro mais rápido: marketing, vendas e funis 
+Módulo 07
+Agente de agendamento
+Um agente que atende seus clientes e realiza agendamentos diretamente no seu Google Agenda.
+Módulo 08
+Agente de atendimento
+Um agente que realiza atendimento do seu fluxo de leads ou clientes. Pode ser usado como canal de suporte ou como central de informações. Repassa o caso para atendimento humano sempre que necessário.
+Módulo 09
+Agente de follow-up
+Monte uma sequência automática com diferentes mensagens de follow-up, mantendo seus leads aquecidos ou reengajando contatos que já estavam frios 
+Módulo 12
+Página de vendas que converte 
+Crie no Lovable uma página de vendas completa — estrutura, copy e call to action — usando IA para escrever e ajustar cada seção 
+Módulo 11
+CRM inteligente que lê seus leads 
+Construa no Lovable um CRM conectado a seus agentes, que mostra qual é o status de seus leads e clientes – e como tratar cada um 
+Módulo 10
+Assistente de produção de conteúdo 
+Crie um agente que gera carrosséis com o tom de voz do seu negócio, alimentado por um briefing que você configura, aumentando sua presença nas redes sociais
+Módulo 13
+Os agentes mais usados do MyHUB.IA
+Aprenda a usar os mais de 80 agentes prontos para usar do MyHUB.IA, que podem criar apresentações, dashboards, contratos, painéis financeiros e muito mais!
+QUERO FAZER MINHA MATRÍCULA
+BÔNUS DE LANÇAMENTO:
+QUERO FAZER MINHA MATRÍCULA
+ESSE NÃO É UM CURSO FOCADO EM DESENVOLVEDORES.
+NA VERDADE, É PARA TODOS QUE:
+Planejam automatizar tudo que pode ser automatizado
+Não suportam mais fazer tarefas mecânicas e repetitivas
+Querem usar ferramentas de IA para ter mais tempo livre
+Desejam ter times mais enxutos e negócios mais lucrativos
+Já entenderam que dominar a IA é essencial para ter futuro
+Desejam criar agentes de IA mesmo sem ser desenvolvedor.
+QUERO FAZER MINHA MATRÍCULA
+12X de
+R$
+167
+QUERO GARANTIR MINHA VAGA
+- Curso com 10h de aulas gravadas
+- 12h de aulas ao vivo (em 8 lives)
+- Módulo de nivelamento para iniciantes
+- Bootcamp de IA para os 500 primeiros
+- Fábrica de Agentes + Templates
++
++ Acesso às 18 melhores IAs disponíveis
++ 80 agentes prontos para usar
++ Super Agente
++ Comunidade
+SUPER COMBO - SÓ 500 VAGAS
+CONDIÇÃO ESPECIAL LIMITADA
+© Copyright 2026 Grupo Primo. Todos os direitos reservados. 
+Políticas de privacidade
+Se você se inscrever no Curso Automatizando Tudo com IA e chegar à conclusão de que esse produto não é sob medida para você, não tem problema.
+Temos tanta confiança na qualidade que garantimos 7 dias para você testá-lo à vontade: se não gostar, basta solicitar o reembolso que devolvemos tudo que você pagou!
+GARANTIA INCONDICIONAL
+Quais são as formas de pagamento?
+Posso efetuar o pagamento com cartão de crédito de um terceiro?
+Esse curso é para quem está começando do zero?
+Preciso saber programar?
+Preciso ter equipe?
+Serve para negócios pequenos?
+O curso é só teoria ou tem prática?
+Vou receber algo pronto ou preciso criar tudo sozinho?
+E se eu tiver dificuldade para implementar?
+Esse curso serve para o meu tipo de negócio?
+Ainda não recebi login e senha; aconteceu algo errado?
+Por quanto tempo terei acesso ao curso?
+Como sei se terei direito a participar do Bootcamp IA na Prática?
+Dúvidas?
+As dúvidas mais comuns de quem quer automatizar com IA 
+Aprenda a criar os Agentes de IA 
+mais usados nas empresas para:
+*Confira o regulamento
+DESCONTO E SUPER BÔNUS PARA OS 500 PRIMEIROS ALUNOS!
+O 1º CURSO de IA 
+do Sérgio Sacani!
+Não é só um curso. Você também ganha:
+Acesso às 18 ferramentas de IA mais avançadas do mundo para criar textos, imagens, vídeos e posts
+Templates para você criar agentes de IA super complexos em poucos minutos
+Módulo de nivelamento para você acompanhar o curso mesmo que não saiba nada de IA hoje
+Bônus Exclusivo para os 500 primeiros:
+Participe do Bootcamp IA na Prática e vire um mestre no assunto em 2 dias!
+QUERO FAZER MINHA MATRÍCULA
+</v>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>SCRUM Planejamento e organização PVRV</v>
+      </c>
+      <c r="B30" t="str">
+        <v>to do</v>
+      </c>
+      <c r="C30" t="str">
+        <v>1792159868768</v>
+      </c>
+      <c r="D30" t="str">
+        <v>pvrv</v>
+      </c>
+      <c r="E30" t="str">
+        <v>16/10/2026</v>
+      </c>
+      <c r="F30" t="str">
+        <v>16/10/2026</v>
+      </c>
+      <c r="G30" t="str" xml:space="preserve">
+        <v xml:space="preserve"># SCRUM Planejamento e organização PVRV
+- [ ] Planejamento financeiro (Financial APP)
+  - [x] Dezembro
+  - [x] Janeiro
+  - [ ] Fevereiro
+  - [ ] Março
+  - [ ] Abril
+  - [ ] Maio
+  - [ ] Junho
+  - [ ] Julho
+  - [ ] Agosto
+  - [ ] Setembro
+  - [ ] Outubro
+  - [ ] Novembro
+  - [ ] Dezembro
+- [x] Planilhas Horarios + Planilha de controle financeiro + Planilhas de treinos
+- [x] planilha de contas a pagar do aluguel em Niterói
+- [x] Planilha de gasto com transporte publico CG x Niteroi
+- [x] requisitos, responsabilidades e atividades na PLC ONS como guia no Word ou Obsidian
+- [ ] passar a limpo screenshots e anotações do caderno para os blogs
+- [ ] Planejamento Financeiro, trabalho PJ e MEI
+- [ ] Prospera MEI - R$ 5000,00 de PIX após quitação das dívidas
+- [ ] PJ como MICRO Empresa de Ciencia de dados, Tecnologia e Engenharia Elétrica
+  - Serviços de modelagem de rede com pandapower e python
+  - Modelagem e Segurança de Banco de Dados
+  - Dashboards e análise de dados de series temporais com modelos de regressão linear, classificação e recomendação
+  - Desenvolvimento de websites (landing pages), Aplicativos  e Softwares Desktop com NextJS, Flutter e Pyqt6
+---
+---
+💡 Dicas práticas
+  &gt; Execute em ciclos curtos: rodar script → validar → corrigir → repetir
+---
+# KANBAN + SCRUM + Organização + Planejamento + metodologia ágil
+Aguardando envio
+Pendências | importante
+Concluído
+- Entregas ageis
+- Kanban para divisão de tarefas BACKLOG, IN PROGRESS, TESTING e CONCLUIDO
+### Gerenciamento de Tempo e Prioridades
+- Pomodoros: 50/10
+- Divisão de tarefas em atividades gerenciais
+- Matriz Eiseingher: Urgente e Não urgente
+- Eat the frog first
+- Prioridade de 3 tarefas principais do dia
+### Planejamento e Metas
+- Planner otimizado com rotinas automatizadas toda segunda e sexta
+- Tarefas com entrega com datas claras e acompanhmento do processo em tempo real
+---
+### 🧠 Diário de Bordo
+- Postagens em blog com Jupyter Notebooks e relatórios em Quarto
+- Bloqueios?
+  - Falta de rotina x Organização e Planejamento
+  - Abstinencia de maconha de 4 dias. Fumei domingo e segunda para aliviar, mas me deu sono e apenas tesão
+- Questões emocionais?
+  - Falta de foco e clareza no que seguir nos estudos: Ciência de Dados e Eng. Elétrica
+  - Falta de segurança em mim mesmo
+---
+</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G30"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/batcaverna/planilhas/kanban.xlsx
+++ b/batcaverna/planilhas/kanban.xlsx
@@ -427,7 +427,7 @@
         <v>UFF - Minicurso Circuitos Eletricos CC</v>
       </c>
       <c r="B2" t="str">
-        <v>in progress</v>
+        <v>projetos parados</v>
       </c>
       <c r="C2" t="str">
         <v>868d3j5vf</v>
@@ -439,7 +439,7 @@
         <v>09/01/2024</v>
       </c>
       <c r="F2" t="str">
-        <v>16/09/2026</v>
+        <v>19/10/2026</v>
       </c>
       <c r="G2" t="str" xml:space="preserve">
         <v xml:space="preserve"># TCC Pedro Victor
@@ -1183,7 +1183,7 @@
         <v>08/12/2025</v>
       </c>
       <c r="F6" t="str">
-        <v>18/07/2026</v>
+        <v>19/10/2026</v>
       </c>
       <c r="G6" t="str" xml:space="preserve">
         <v xml:space="preserve"># O Plano Espiritual - Como Deus desenhou o mundo?
@@ -1254,6 +1254,8 @@
 ## Corpo Humano
 ## Treinos: Calistenia, Musculação, Corrida, Futebol, Alongamentos, Yoga e Karate
 ---
+# PV Batcaverna NOTES 2026
+---
 # Jejum de dopamina e Controle de Habitos
 ---
 o vício em redes sociais e a "dopamina barata", oferecendo estratégias práticas para retomar o controle da rotina e diminuir a ansiedade causada pelo tempo excessivo de tela.
@@ -1327,8 +1329,14 @@
 - [ ] Entender os exercicios resolvidos dos livros
 - [ ] 3 de Circuitos Elétricos
 - [ ] 2 de revisão
+---
+## Futebol
+## Nutrição + Equilibrio do corpo humano
+## Probabilidades e palpites no futebol
+---
 ## 💪 Corpo
 Treino ou caminhada (20–30 min)
+Treinos: Calistenia, Musculação, Corrida, Futebol, Alongamentos, Yoga e Karate
 ## 🌙 Ritual de Encerramento do Dia
 ✔ O que avancei:
 ---
@@ -1625,7 +1633,7 @@
         <v>CLAUDE CODE WEB</v>
       </c>
       <c r="B9" t="str">
-        <v>agentes (c3po, jarvis, groundon, lumina Aurora)</v>
+        <v>testing</v>
       </c>
       <c r="C9" t="str">
         <v>1768308273883</v>
@@ -1637,7 +1645,7 @@
         <v>13/01/2026</v>
       </c>
       <c r="F9" t="str">
-        <v>12/06/2026</v>
+        <v>19/10/2026</v>
       </c>
       <c r="G9" t="str" xml:space="preserve">
         <v xml:space="preserve">## Assistende de AI - Claude Sonnet
@@ -3597,50 +3605,24 @@
     </row>
     <row r="26" xml:space="preserve">
       <c r="A26" t="str">
-        <v>Copa do Mundo 2026</v>
+        <v>CIÊNCIA DE DADOS - Graduação BACHARELADO - UFF</v>
       </c>
       <c r="B26" t="str">
-        <v>testing</v>
+        <v>to do</v>
       </c>
       <c r="C26" t="str">
-        <v>1781658844848</v>
+        <v>1785443003530</v>
       </c>
       <c r="D26" t="str">
-        <v>ons</v>
+        <v>data_science</v>
       </c>
       <c r="E26" t="str">
-        <v>16/06/2026</v>
+        <v>30/07/2026</v>
       </c>
       <c r="F26" t="str">
-        <v>06/07/2026</v>
+        <v>16/09/2026</v>
       </c>
       <c r="G26" t="str" xml:space="preserve">
-        <v xml:space="preserve">## Futebol
-## Nutrição + Equilibrio do corpo humano
-## Probabilidades e palpites no futebol
-## Treinos: Calistenia, Musculação, Corrida, Futebol, Alongamentos, Yoga e Karate</v>
-      </c>
-    </row>
-    <row r="27" xml:space="preserve">
-      <c r="A27" t="str">
-        <v>CIÊNCIA DE DADOS - Graduação BACHARELADO - UFF</v>
-      </c>
-      <c r="B27" t="str">
-        <v>to do</v>
-      </c>
-      <c r="C27" t="str">
-        <v>1785443003530</v>
-      </c>
-      <c r="D27" t="str">
-        <v>data_science</v>
-      </c>
-      <c r="E27" t="str">
-        <v>30/07/2026</v>
-      </c>
-      <c r="F27" t="str">
-        <v>16/09/2026</v>
-      </c>
-      <c r="G27" t="str" xml:space="preserve">
         <v xml:space="preserve"># Curso: INTELIGÊNCIA ARTIFICIAL E CIÊNCIA DE DADOS
 - GRAU - Graduação
 ---
@@ -3693,26 +3675,26 @@
 </v>
       </c>
     </row>
-    <row r="28" xml:space="preserve">
-      <c r="A28" t="str">
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
         <v>Estatistica para Ciencia de Dados</v>
       </c>
-      <c r="B28" t="str">
+      <c r="B27" t="str">
         <v>to do</v>
       </c>
-      <c r="C28" t="str">
+      <c r="C27" t="str">
         <v>1785951514953</v>
       </c>
-      <c r="D28" t="str">
+      <c r="D27" t="str">
         <v>uff</v>
       </c>
-      <c r="E28" t="str">
+      <c r="E27" t="str">
         <v>05/08/2026</v>
       </c>
-      <c r="F28" t="str">
+      <c r="F27" t="str">
         <v>05/08/2026</v>
       </c>
-      <c r="G28" t="str" xml:space="preserve">
+      <c r="G27" t="str" xml:space="preserve">
         <v xml:space="preserve">## Base de dados publicas
 - NASA
 - Pokemon
@@ -3761,26 +3743,26 @@
 </v>
       </c>
     </row>
-    <row r="29" xml:space="preserve">
-      <c r="A29" t="str">
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
         <v>Agente de IA - Sergio Sacani</v>
       </c>
-      <c r="B29" t="str">
+      <c r="B28" t="str">
         <v>projetos parados</v>
       </c>
-      <c r="C29" t="str">
+      <c r="C28" t="str">
         <v>1787112771173</v>
       </c>
-      <c r="D29" t="str">
+      <c r="D28" t="str">
         <v>ons</v>
       </c>
-      <c r="E29" t="str">
+      <c r="E28" t="str">
         <v>19/08/2026</v>
       </c>
-      <c r="F29" t="str">
+      <c r="F28" t="str">
         <v>20/08/2026</v>
       </c>
-      <c r="G29" t="str" xml:space="preserve">
+      <c r="G28" t="str" xml:space="preserve">
         <v xml:space="preserve">## Ferramentas
 - n8n
 - chatgpt x gemini x chatmaritaca
@@ -3888,26 +3870,26 @@
 </v>
       </c>
     </row>
-    <row r="30" xml:space="preserve">
-      <c r="A30" t="str">
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
         <v>SCRUM Planejamento e organização PVRV</v>
       </c>
-      <c r="B30" t="str">
+      <c r="B29" t="str">
         <v>to do</v>
       </c>
-      <c r="C30" t="str">
+      <c r="C29" t="str">
         <v>1792159868768</v>
       </c>
-      <c r="D30" t="str">
+      <c r="D29" t="str">
         <v>pvrv</v>
       </c>
-      <c r="E30" t="str">
+      <c r="E29" t="str">
         <v>16/10/2026</v>
       </c>
-      <c r="F30" t="str">
+      <c r="F29" t="str">
         <v>16/10/2026</v>
       </c>
-      <c r="G30" t="str" xml:space="preserve">
+      <c r="G29" t="str" xml:space="preserve">
         <v xml:space="preserve"># SCRUM Planejamento e organização PVRV
 - [ ] Planejamento financeiro (Financial APP)
   - [x] Dezembro
@@ -3968,6 +3950,30 @@
 </v>
       </c>
     </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>Programação em Lua, Python e Javascript</v>
+      </c>
+      <c r="B30" t="str">
+        <v>in progress</v>
+      </c>
+      <c r="C30" t="str">
+        <v>1792450037255</v>
+      </c>
+      <c r="D30" t="str">
+        <v>web</v>
+      </c>
+      <c r="E30" t="str">
+        <v>19/10/2026</v>
+      </c>
+      <c r="F30" t="str">
+        <v>19/10/2026</v>
+      </c>
+      <c r="G30" t="str" xml:space="preserve">
+        <v xml:space="preserve"># Novo Item
+Descreva aqui o conteúdo...</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:G30"/>

--- a/batcaverna/planilhas/kanban.xlsx
+++ b/batcaverna/planilhas/kanban.xlsx
@@ -733,7 +733,7 @@
         <v>Estágio ONS 2025/2026</v>
       </c>
       <c r="B5" t="str">
-        <v>projetos parados</v>
+        <v>ONS - PLC - 2026</v>
       </c>
       <c r="C5" t="str">
         <v>1764640448116</v>
@@ -745,7 +745,7 @@
         <v>01/12/2025</v>
       </c>
       <c r="F5" t="str">
-        <v>06/07/2026</v>
+        <v>21/10/2026</v>
       </c>
       <c r="G5" t="str" xml:space="preserve">
         <v xml:space="preserve">
@@ -1659,7 +1659,7 @@
         <v>UFF 2026.1</v>
       </c>
       <c r="B10" t="str">
-        <v>to do</v>
+        <v>PVRV - Batcaverna</v>
       </c>
       <c r="C10" t="str">
         <v>1768855939861</v>
@@ -1671,7 +1671,7 @@
         <v>19/01/2026</v>
       </c>
       <c r="F10" t="str">
-        <v>16/10/2026</v>
+        <v>21/10/2026</v>
       </c>
       <c r="G10" t="str" xml:space="preserve">
         <v xml:space="preserve">---
@@ -1874,7 +1874,7 @@
         <v xml:space="preserve">ESTUDOS - Quizz App with AI </v>
       </c>
       <c r="B12" t="str">
-        <v>to do</v>
+        <v>testing</v>
       </c>
       <c r="C12" t="str">
         <v>1770229463843</v>
@@ -1886,7 +1886,7 @@
         <v>04/02/2026</v>
       </c>
       <c r="F12" t="str">
-        <v>16/10/2026</v>
+        <v>21/10/2026</v>
       </c>
       <c r="G12" t="str" xml:space="preserve">
         <v xml:space="preserve">_x000d__x000d_
@@ -1904,7 +1904,7 @@
         <v>Análise de Requisitos - Banco de Dados PLC</v>
       </c>
       <c r="B13" t="str">
-        <v>projetos parados</v>
+        <v>ONS - PLC - 2026</v>
       </c>
       <c r="C13" t="str">
         <v>1770818504733</v>
@@ -1916,7 +1916,7 @@
         <v>11/02/2026</v>
       </c>
       <c r="F13" t="str">
-        <v>17/06/2026</v>
+        <v>21/10/2026</v>
       </c>
       <c r="G13" t="str" xml:space="preserve">
         <v xml:space="preserve">---
@@ -1973,7 +1973,7 @@
         <v>11/02/2026</v>
       </c>
       <c r="F14" t="str">
-        <v>05/08/2026</v>
+        <v>21/10/2026</v>
       </c>
       <c r="G14" t="str" xml:space="preserve">
         <v xml:space="preserve">Curso completo de Eletrônica Analógica Básica
@@ -2554,7 +2554,7 @@
         <v>17/03/2026</v>
       </c>
       <c r="F16" t="str">
-        <v>16/10/2026</v>
+        <v>21/10/2026</v>
       </c>
       <c r="G16" t="str" xml:space="preserve">
         <v xml:space="preserve">## Circuitos Digitais P1
@@ -2666,7 +2666,15 @@
 10 - MEMÓRIAS
 10.1 - CLASSIFICAÇÃO: VOLÁTIL VS NÃO VOLÁTIL
 10.2 - TIPOS: RAM (SRAM, DRAM), ROM, PROM, EEPROM, FLASH
-10.3 - ORGANIZAÇÃO INTERNA: ENDEREÇAMENTO, BARRAMENTOS, TEMPO DE ACESSO</v>
+10.3 - ORGANIZAÇÃO INTERNA: ENDEREÇAMENTO, BARRAMENTOS, TEMPO DE ACESSO
+## Circuitos Eletricos CC
+## Laboratorio de Eng Eletrica e automação
+ - [x] Eletronica
+ - [x] Robotica
+ - [x] Programação em C++
+## Sinais e Sistemas
+## Circuitos CA
+## </v>
       </c>
     </row>
     <row r="17" xml:space="preserve">
@@ -2674,7 +2682,7 @@
         <v>Projetos Desktop PLC ONS 2026</v>
       </c>
       <c r="B17" t="str">
-        <v>to do</v>
+        <v>projetos parados</v>
       </c>
       <c r="C17" t="str">
         <v>1773751533960</v>
@@ -2686,7 +2694,7 @@
         <v>17/03/2026</v>
       </c>
       <c r="F17" t="str">
-        <v>20/08/2026</v>
+        <v>19/10/2026</v>
       </c>
       <c r="G17" t="str" xml:space="preserve">
         <v xml:space="preserve">
@@ -2857,7 +2865,7 @@
         <v>Ementas - UFF</v>
       </c>
       <c r="B19" t="str">
-        <v>to do</v>
+        <v>PVRV - Batcaverna</v>
       </c>
       <c r="C19" t="str">
         <v>1777067813617</v>
@@ -2869,7 +2877,7 @@
         <v>24/04/2026</v>
       </c>
       <c r="F19" t="str">
-        <v>16/10/2026</v>
+        <v>21/10/2026</v>
       </c>
       <c r="G19" t="str" xml:space="preserve">
         <v xml:space="preserve">
@@ -3230,7 +3238,7 @@
         <v>Engenharia Elétrica UFF 2026</v>
       </c>
       <c r="B20" t="str">
-        <v>to do</v>
+        <v>uff - 2026</v>
       </c>
       <c r="C20" t="str">
         <v>1777484682216</v>
@@ -3242,7 +3250,7 @@
         <v>29/04/2026</v>
       </c>
       <c r="F20" t="str">
-        <v>25/07/2026</v>
+        <v>21/10/2026</v>
       </c>
       <c r="G20" t="str" xml:space="preserve">
         <v xml:space="preserve">---
@@ -3294,7 +3302,7 @@
         <v xml:space="preserve">Relatórios PDF, OverLeaf, Quarto e Artigos Científicos </v>
       </c>
       <c r="B21" t="str">
-        <v>to do</v>
+        <v>projetos parados</v>
       </c>
       <c r="C21" t="str">
         <v>1778242830252</v>
@@ -3306,7 +3314,7 @@
         <v>08/05/2026</v>
       </c>
       <c r="F21" t="str">
-        <v>05/08/2026</v>
+        <v>19/10/2026</v>
       </c>
       <c r="G21" t="str" xml:space="preserve">
         <v xml:space="preserve"># Novo Item
@@ -3620,7 +3628,7 @@
         <v>30/07/2026</v>
       </c>
       <c r="F26" t="str">
-        <v>16/09/2026</v>
+        <v>21/10/2026</v>
       </c>
       <c r="G26" t="str" xml:space="preserve">
         <v xml:space="preserve"># Curso: INTELIGÊNCIA ARTIFICIAL E CIÊNCIA DE DADOS
@@ -3680,7 +3688,7 @@
         <v>Estatistica para Ciencia de Dados</v>
       </c>
       <c r="B27" t="str">
-        <v>to do</v>
+        <v>uff - 2026</v>
       </c>
       <c r="C27" t="str">
         <v>1785951514953</v>
@@ -3692,7 +3700,7 @@
         <v>05/08/2026</v>
       </c>
       <c r="F27" t="str">
-        <v>05/08/2026</v>
+        <v>21/10/2026</v>
       </c>
       <c r="G27" t="str" xml:space="preserve">
         <v xml:space="preserve">## Base de dados publicas
@@ -3952,7 +3960,7 @@
     </row>
     <row r="30" xml:space="preserve">
       <c r="A30" t="str">
-        <v>Programação em Lua, Python e Javascript</v>
+        <v>Programação em  Python, C++, Javascript e Lua</v>
       </c>
       <c r="B30" t="str">
         <v>in progress</v>
@@ -3961,17 +3969,42 @@
         <v>1792450037255</v>
       </c>
       <c r="D30" t="str">
-        <v>web</v>
+        <v>data_science</v>
       </c>
       <c r="E30" t="str">
         <v>19/10/2026</v>
       </c>
       <c r="F30" t="str">
-        <v>19/10/2026</v>
+        <v>21/10/2026</v>
       </c>
       <c r="G30" t="str" xml:space="preserve">
-        <v xml:space="preserve"># Novo Item
-Descreva aqui o conteúdo...</v>
+        <v xml:space="preserve"># Python
+ - [x] Análise de Dados
+ - [x] Streamlit
+ - [x] PyQt6
+ - [x] Robo RPA
+ - [x] Bots web scrapping
+ - [x] Exercicios de estrutura de dados 
+# Javascript
+ - [x] NextJS -&gt; Vercel
+ - [x] SEO e Acessibilidade
+ - [x] Gerenciamento de estado
+ - [x] CRUD x Dashboards x Landing pages
+ - [x] astroblog - pedrov12
+ - [x] SEP para leigos
+# Lua
+ - [x] Love 2D
+ - [x] Roblox Studio
+# C++
+ - [x] Variaveis
+ - [x] Estutura de repetição e condição
+ - [x] POO
+ - [x] Structs
+ - [x] Ponteiros
+ - [x] Estrutura de dados
+ - [x] Leitura e escrita de arquivos .txt e .csv
+ - [x] Robotica para Iniciantes
+</v>
       </c>
     </row>
   </sheetData>

--- a/batcaverna/planilhas/kanban.xlsx
+++ b/batcaverna/planilhas/kanban.xlsx
@@ -733,7 +733,7 @@
         <v>Estágio ONS 2025/2026</v>
       </c>
       <c r="B5" t="str">
-        <v>ONS - PLC - 2026</v>
+        <v>completed</v>
       </c>
       <c r="C5" t="str">
         <v>1764640448116</v>
@@ -745,7 +745,7 @@
         <v>01/12/2025</v>
       </c>
       <c r="F5" t="str">
-        <v>21/10/2026</v>
+        <v>28/10/2026</v>
       </c>
       <c r="G5" t="str" xml:space="preserve">
         <v xml:space="preserve">
@@ -1659,7 +1659,7 @@
         <v>UFF 2026.1</v>
       </c>
       <c r="B10" t="str">
-        <v>PVRV - Batcaverna</v>
+        <v>uff - 2026</v>
       </c>
       <c r="C10" t="str">
         <v>1768855939861</v>
@@ -1671,7 +1671,7 @@
         <v>19/01/2026</v>
       </c>
       <c r="F10" t="str">
-        <v>21/10/2026</v>
+        <v>28/10/2026</v>
       </c>
       <c r="G10" t="str" xml:space="preserve">
         <v xml:space="preserve">---
@@ -1874,7 +1874,7 @@
         <v xml:space="preserve">ESTUDOS - Quizz App with AI </v>
       </c>
       <c r="B12" t="str">
-        <v>testing</v>
+        <v>to do</v>
       </c>
       <c r="C12" t="str">
         <v>1770229463843</v>
@@ -1886,7 +1886,7 @@
         <v>04/02/2026</v>
       </c>
       <c r="F12" t="str">
-        <v>21/10/2026</v>
+        <v>28/10/2026</v>
       </c>
       <c r="G12" t="str" xml:space="preserve">
         <v xml:space="preserve">_x000d__x000d_
@@ -2682,7 +2682,7 @@
         <v>Projetos Desktop PLC ONS 2026</v>
       </c>
       <c r="B17" t="str">
-        <v>projetos parados</v>
+        <v>completed</v>
       </c>
       <c r="C17" t="str">
         <v>1773751533960</v>
@@ -2694,7 +2694,7 @@
         <v>17/03/2026</v>
       </c>
       <c r="F17" t="str">
-        <v>19/10/2026</v>
+        <v>28/10/2026</v>
       </c>
       <c r="G17" t="str" xml:space="preserve">
         <v xml:space="preserve">
@@ -2865,7 +2865,7 @@
         <v>Ementas - UFF</v>
       </c>
       <c r="B19" t="str">
-        <v>PVRV - Batcaverna</v>
+        <v>uff - 2026</v>
       </c>
       <c r="C19" t="str">
         <v>1777067813617</v>
@@ -2877,7 +2877,7 @@
         <v>24/04/2026</v>
       </c>
       <c r="F19" t="str">
-        <v>21/10/2026</v>
+        <v>28/10/2026</v>
       </c>
       <c r="G19" t="str" xml:space="preserve">
         <v xml:space="preserve">
@@ -3250,7 +3250,7 @@
         <v>29/04/2026</v>
       </c>
       <c r="F20" t="str">
-        <v>21/10/2026</v>
+        <v>28/10/2026</v>
       </c>
       <c r="G20" t="str" xml:space="preserve">
         <v xml:space="preserve">---
@@ -3756,7 +3756,7 @@
         <v>Agente de IA - Sergio Sacani</v>
       </c>
       <c r="B28" t="str">
-        <v>projetos parados</v>
+        <v>completed</v>
       </c>
       <c r="C28" t="str">
         <v>1787112771173</v>
@@ -3768,7 +3768,7 @@
         <v>19/08/2026</v>
       </c>
       <c r="F28" t="str">
-        <v>20/08/2026</v>
+        <v>28/10/2026</v>
       </c>
       <c r="G28" t="str" xml:space="preserve">
         <v xml:space="preserve">## Ferramentas
